--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484730_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484730_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.768700000000001</v>
+        <v>7.2005</v>
       </c>
       <c r="E2" t="n">
-        <v>8.026199999999999</v>
+        <v>5.5904</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7424</v>
+        <v>1.6102</v>
       </c>
       <c r="G2" t="n">
         <v>5.5962</v>
@@ -610,13 +610,13 @@
         <v>1.887</v>
       </c>
       <c r="S2" t="n">
-        <v>4.8332</v>
+        <v>2.2651</v>
       </c>
       <c r="T2" t="n">
-        <v>4.7973</v>
+        <v>2.3615</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0359</v>
+        <v>-0.0963</v>
       </c>
       <c r="V2" t="n">
         <v>1.2262</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.7889</v>
+        <v>6.5994</v>
       </c>
       <c r="E3" t="n">
-        <v>6.6764</v>
+        <v>7.2223</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8875</v>
+        <v>-0.6229</v>
       </c>
       <c r="G3" t="n">
         <v>3.5382</v>
@@ -688,13 +688,13 @@
         <v>2.0757</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3186</v>
+        <v>1.1291</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3144</v>
+        <v>1.8603</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9957</v>
+        <v>-0.7312</v>
       </c>
       <c r="V3" t="n">
         <v>0.7999000000000001</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1094</v>
+        <v>2.9411</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8042</v>
+        <v>2.3502</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3052</v>
+        <v>0.591</v>
       </c>
       <c r="G4" t="n">
         <v>-1.2086</v>
@@ -766,13 +766,13 @@
         <v>2.6418</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2163</v>
+        <v>1.048</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5472</v>
+        <v>1.0932</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6691</v>
+        <v>-0.0452</v>
       </c>
       <c r="V4" t="n">
         <v>2.3469</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. RODILLA ALCAIDE</t>
+          <t>R. MALLIK BOUNAD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9354</v>
+        <v>2.5758</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3963</v>
+        <v>1.5928</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5391</v>
+        <v>0.983</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7389</v>
+        <v>1.0531</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.059</v>
+        <v>-0.3107</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3202</v>
+        <v>1.3638</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4863</v>
+        <v>2.2999</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.8554</v>
+        <v>0.8929</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3417</v>
+        <v>1.4069</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2252</v>
+        <v>-1.2467</v>
       </c>
       <c r="N5" t="n">
         <v>-1.2036</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0216</v>
+        <v>-0.0431</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5661</v>
+        <v>0.3774</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5096</v>
+        <v>2.2644</v>
       </c>
       <c r="S5" t="n">
-        <v>1.6477</v>
+        <v>1.1453</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6083</v>
+        <v>1.1799</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0394</v>
+        <v>-0.0347</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4604</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.2152</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. BOSCH ROIG</t>
+          <t>M. RODILLA ALCAIDE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.208</v>
+        <v>2.4747</v>
       </c>
       <c r="E6" t="n">
-        <v>4.0304</v>
+        <v>1.9092</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.8224</v>
+        <v>0.5655</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0488</v>
+        <v>-0.7389</v>
       </c>
       <c r="H6" t="n">
-        <v>2.6726</v>
+        <v>-2.059</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.6238</v>
+        <v>1.3202</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8313</v>
+        <v>0.4863</v>
       </c>
       <c r="K6" t="n">
-        <v>3.6978</v>
+        <v>-0.8554</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.8664</v>
+        <v>1.3417</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.7826</v>
+        <v>-1.2252</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0252</v>
+        <v>-1.2036</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7574</v>
+        <v>-0.0216</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7548</v>
+        <v>0.5661</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7548</v>
+        <v>1.5096</v>
       </c>
       <c r="S6" t="n">
-        <v>1.529</v>
+        <v>1.187</v>
       </c>
       <c r="T6" t="n">
-        <v>2.1991</v>
+        <v>1.1211</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6701</v>
+        <v>0.0659</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1245</v>
+        <v>1.4604</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1245</v>
+        <v>0.2152</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. MALLIK BOUNAD</t>
+          <t>J. BOSCH ROIG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0349</v>
+        <v>1.8506</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1313</v>
+        <v>3.6995</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9036</v>
+        <v>-1.8488</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0531</v>
+        <v>0.0488</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3107</v>
+        <v>2.6726</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3638</v>
+        <v>-2.6238</v>
       </c>
       <c r="J7" t="n">
-        <v>2.2999</v>
+        <v>1.8313</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8929</v>
+        <v>3.6978</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4069</v>
+        <v>-1.8664</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2467</v>
+        <v>-1.7826</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2036</v>
+        <v>-1.0252</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0431</v>
+        <v>-0.7574</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3774</v>
+        <v>0.7548</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2644</v>
+        <v>0.7548</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3956</v>
+        <v>1.1716</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2816</v>
+        <v>1.8681</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.114</v>
+        <v>-0.6965</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.1245</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.1245</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5249</v>
+        <v>0.7643</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8188</v>
+        <v>1.1111</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2939</v>
+        <v>-0.3468</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0501</v>
@@ -1078,13 +1078,13 @@
         <v>1.3209</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5185</v>
+        <v>0.7579</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4267</v>
+        <v>0.7191</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0917</v>
+        <v>0.0388</v>
       </c>
       <c r="V8" t="n">
         <v>0.6226</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4809</v>
+        <v>-0.2596</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0058</v>
+        <v>0.189</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4751</v>
+        <v>-0.4486</v>
       </c>
       <c r="G9" t="n">
         <v>-1.1211</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0176</v>
+        <v>0.239</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.1949</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0176</v>
+        <v>0.0441</v>
       </c>
       <c r="V9" t="n">
         <v>0.6226</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1883</v>
+        <v>-2.2425</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4835</v>
+        <v>-2.7758</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2952</v>
+        <v>0.5333</v>
       </c>
       <c r="G10" t="n">
         <v>-3.1658</v>
@@ -1234,13 +1234,13 @@
         <v>2.0757</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4114</v>
+        <v>1.3572</v>
       </c>
       <c r="T10" t="n">
-        <v>1.5495</v>
+        <v>1.2572</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1381</v>
+        <v>0.1</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6226</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5903</v>
+        <v>-2.6025</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7648</v>
+        <v>-0.8034</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8256</v>
+        <v>-1.7991</v>
       </c>
       <c r="G11" t="n">
         <v>-3.0154</v>
@@ -1312,13 +1312,13 @@
         <v>0.7548</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7383</v>
+        <v>0.7261</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9464</v>
+        <v>0.9077</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2081</v>
+        <v>-0.1816</v>
       </c>
       <c r="V11" t="n">
         <v>-0.1245</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.6062</v>
+        <v>-5.5034</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3811</v>
+        <v>-2.5428</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.2252</v>
+        <v>-2.9606</v>
       </c>
       <c r="G12" t="n">
         <v>-6.0816</v>
@@ -1390,13 +1390,13 @@
         <v>1.6983</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9776</v>
+        <v>0.1252</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1451</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.1228</v>
+        <v>-0.8582</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3018</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>13.5045</v>
+        <v>13.7984</v>
       </c>
       <c r="E13" t="n">
-        <v>17.2484</v>
+        <v>17.5425</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.7442</v>
+        <v>-3.743799999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-5.145200000000001</v>
@@ -1438,7 +1438,7 @@
         <v>-2.7626</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.382499999999999</v>
+        <v>-2.3825</v>
       </c>
       <c r="J13" t="n">
         <v>11.9796</v>
@@ -1468,19 +1468,19 @@
         <v>16.983</v>
       </c>
       <c r="S13" t="n">
-        <v>10.8574</v>
+        <v>11.1515</v>
       </c>
       <c r="T13" t="n">
-        <v>13.2524</v>
+        <v>13.5464</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.3951</v>
+        <v>-2.3949</v>
       </c>
       <c r="V13" t="n">
         <v>5.9052</v>
       </c>
       <c r="W13" t="n">
-        <v>7.112400000000001</v>
+        <v>7.1124</v>
       </c>
       <c r="X13" t="n">
         <v>-1.2072</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. LOPEZ RICO</t>
+          <t>J. DE YRAOLAGOTIA TELLO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8685</v>
+        <v>1.106</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1098</v>
+        <v>3.9549</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2413</v>
+        <v>-2.8489</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3927</v>
+        <v>1.5905</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5525</v>
+        <v>1.8634</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8401999999999999</v>
+        <v>-0.2729</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4892</v>
+        <v>4.8899</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4069</v>
+        <v>4.1892</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0823</v>
+        <v>0.7007</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9035</v>
+        <v>-3.2994</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1456</v>
+        <v>-2.3258</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7579</v>
+        <v>-0.9735</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3774</v>
+        <v>0.7548</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3774</v>
+        <v>2.6418</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0228</v>
+        <v>-2.0392</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6206</v>
+        <v>0.0276</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5978</v>
+        <v>-2.0668</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.9244</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.9244</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.9244</v>
+        <v>-0.1245</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. PEREZ DIEZ</t>
+          <t>M. LOPEZ RICO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1931</v>
+        <v>0.9530999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1929</v>
+        <v>1.0381</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0002</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5093</v>
+        <v>1.3927</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7645999999999999</v>
+        <v>0.5525</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2553</v>
+        <v>0.8401999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2952</v>
+        <v>0.4892</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2044</v>
+        <v>0.4069</v>
       </c>
       <c r="L15" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.0823</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7859</v>
+        <v>0.9035</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4398</v>
+        <v>0.1456</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3461</v>
+        <v>0.7579</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5661</v>
+        <v>0.3774</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5096</v>
+        <v>0.3774</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2422</v>
+        <v>0.1074</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8411999999999999</v>
+        <v>0.5489000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.599</v>
+        <v>-0.4414</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1245</v>
+        <v>-0.9244</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1245</v>
+        <v>-0.9244</v>
       </c>
     </row>
     <row r="16">
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. CALERO SEVILLANO</t>
+          <t>M. PEREZ DIEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8633999999999999</v>
+        <v>0.7119</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0501</v>
+        <v>0.6082</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9135</v>
+        <v>0.1037</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0808</v>
+        <v>0.5093</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1941</v>
+        <v>0.7645999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2749</v>
+        <v>-0.2553</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4427</v>
+        <v>1.2952</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1487</v>
+        <v>1.2044</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5914</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5235</v>
+        <v>-0.7859</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3428</v>
+        <v>-0.4398</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8663</v>
+        <v>-0.3461</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1322</v>
+        <v>0.5661</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1322</v>
+        <v>1.5096</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3685</v>
+        <v>-0.239</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3926</v>
+        <v>0.2566</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7612</v>
+        <v>-0.4955</v>
       </c>
       <c r="V17" t="n">
-        <v>0.019</v>
+        <v>-0.1245</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.019</v>
+        <v>-0.1245</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. DE YRAOLAGOTIA TELLO</t>
+          <t>J. CALERO SEVILLANO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0114</v>
+        <v>0.57</v>
       </c>
       <c r="E18" t="n">
-        <v>3.1754</v>
+        <v>-0.0501</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.164</v>
+        <v>0.6201</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5905</v>
+        <v>0.0808</v>
       </c>
       <c r="H18" t="n">
-        <v>1.8634</v>
+        <v>-0.1941</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2729</v>
+        <v>0.2749</v>
       </c>
       <c r="J18" t="n">
-        <v>4.8899</v>
+        <v>-0.4427</v>
       </c>
       <c r="K18" t="n">
-        <v>4.1892</v>
+        <v>0.1487</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7007</v>
+        <v>-0.5914</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.2994</v>
+        <v>0.5235</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.3258</v>
+        <v>-0.3428</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9735</v>
+        <v>0.8663</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7548</v>
+        <v>1.1322</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.6418</v>
+        <v>1.1322</v>
       </c>
       <c r="S18" t="n">
-        <v>-3.1338</v>
+        <v>-0.6619</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7519</v>
+        <v>0.3926</v>
       </c>
       <c r="U18" t="n">
-        <v>-2.3819</v>
+        <v>-1.0545</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.019</v>
       </c>
       <c r="W18" t="n">
-        <v>0.9244</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1245</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6995</v>
+        <v>-0.6574</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7133</v>
+        <v>1.8107</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.4128</v>
+        <v>-2.468</v>
       </c>
       <c r="G19" t="n">
         <v>3.3523</v>
@@ -1936,13 +1936,13 @@
         <v>2.2644</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.0968</v>
+        <v>-2.0546</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0312</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.0656</v>
+        <v>-2.1209</v>
       </c>
       <c r="V19" t="n">
         <v>0.4981</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5632</v>
+        <v>-2.0412</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.8218</v>
+        <v>-2.4321</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2586</v>
+        <v>0.3909</v>
       </c>
       <c r="G20" t="n">
         <v>-2.1564</v>
@@ -2014,13 +2014,13 @@
         <v>0.3774</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7842</v>
+        <v>-0.2622</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4115</v>
+        <v>-0.0218</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3727</v>
+        <v>-0.2404</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9726</v>
+        <v>-2.8524</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3053</v>
+        <v>1.1104</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.278</v>
+        <v>-3.9629</v>
       </c>
       <c r="G21" t="n">
         <v>0.0533</v>
@@ -2092,13 +2092,13 @@
         <v>2.0757</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.6677</v>
+        <v>-1.5475</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6183</v>
+        <v>0.4235</v>
       </c>
       <c r="U21" t="n">
-        <v>-2.2861</v>
+        <v>-1.971</v>
       </c>
       <c r="V21" t="n">
         <v>-2.4904</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. PUJALTE MIRA</t>
+          <t>V. VICENT TORTOSA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2975</v>
+        <v>-2.9262</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5241</v>
+        <v>1.6821</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7733</v>
+        <v>-4.6083</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9343</v>
+        <v>2.1499</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8155</v>
+        <v>-0.0305</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1189</v>
+        <v>2.1804</v>
       </c>
       <c r="J22" t="n">
-        <v>1.0654</v>
+        <v>4.9782</v>
       </c>
       <c r="K22" t="n">
-        <v>0.925</v>
+        <v>2.2139</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1404</v>
+        <v>2.7642</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.9998</v>
+        <v>-2.8283</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.7405</v>
+        <v>-2.2445</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2593</v>
+        <v>-0.5838</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.887</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.774</v>
+        <v>-2.8305</v>
       </c>
       <c r="R22" t="n">
-        <v>1.887</v>
+        <v>2.0757</v>
       </c>
       <c r="S22" t="n">
-        <v>0.271</v>
+        <v>-1.6874</v>
       </c>
       <c r="T22" t="n">
-        <v>1.1844</v>
+        <v>0.176</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9134</v>
+        <v>-1.8634</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.7471</v>
+        <v>-2.6339</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.7471</v>
+        <v>-1.9923</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>V. VICENT TORTOSA</t>
+          <t>J. PUJALTE MIRA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.2133</v>
+        <v>-3.9025</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7077</v>
+        <v>-2.2062</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.921</v>
+        <v>-1.6963</v>
       </c>
       <c r="G23" t="n">
-        <v>2.1499</v>
+        <v>-0.9343</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0305</v>
+        <v>-0.8155</v>
       </c>
       <c r="I23" t="n">
-        <v>2.1804</v>
+        <v>-0.1189</v>
       </c>
       <c r="J23" t="n">
-        <v>4.9782</v>
+        <v>1.0654</v>
       </c>
       <c r="K23" t="n">
-        <v>2.2139</v>
+        <v>0.925</v>
       </c>
       <c r="L23" t="n">
-        <v>2.7642</v>
+        <v>0.1404</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.8283</v>
+        <v>-1.9998</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.2445</v>
+        <v>-1.7405</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5838</v>
+        <v>-0.2593</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.7548</v>
+        <v>-1.887</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.8305</v>
+        <v>-3.774</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0757</v>
+        <v>1.887</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.9745</v>
+        <v>-0.334</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7984</v>
+        <v>0.5024</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.1761</v>
+        <v>-0.8364</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.6339</v>
+        <v>-0.7471</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.9923</v>
+        <v>-0.7471</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.6287</v>
+        <v>-4.1007</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.3001</v>
+        <v>-3.0078</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3286</v>
+        <v>-1.0929</v>
       </c>
       <c r="G24" t="n">
         <v>-1.8268</v>
@@ -2326,13 +2326,13 @@
         <v>0.7548</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3679</v>
+        <v>-0.8399</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2693</v>
+        <v>0.023</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.0987</v>
+        <v>-0.8629</v>
       </c>
       <c r="V24" t="n">
         <v>-0.3018</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-13.5045</v>
+        <v>-12.2055</v>
       </c>
       <c r="E25" t="n">
-        <v>3.4422</v>
+        <v>3.4421</v>
       </c>
       <c r="F25" t="n">
-        <v>-16.9467</v>
+        <v>-15.6476</v>
       </c>
       <c r="G25" t="n">
         <v>5.145199999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>2.7626</v>
+        <v>2.762599999999999</v>
       </c>
       <c r="I25" t="n">
         <v>2.3826</v>
@@ -2404,16 +2404,16 @@
         <v>15.096</v>
       </c>
       <c r="S25" t="n">
-        <v>-10.8574</v>
+        <v>-9.558300000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>2.3948</v>
+        <v>2.395</v>
       </c>
       <c r="U25" t="n">
-        <v>-13.2525</v>
+        <v>-11.9532</v>
       </c>
       <c r="V25" t="n">
-        <v>-5.905100000000001</v>
+        <v>-5.9051</v>
       </c>
       <c r="W25" t="n">
         <v>0.9054000000000002</v>
